--- a/output/topology_excel/451.xlsx
+++ b/output/topology_excel/451.xlsx
@@ -425,43 +425,58 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G38"/>
+  <dimension ref="A1:J41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>房间ID1</t>
+          <t>房间1</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>房间类型1</t>
+          <t>类型1</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>房间ID2</t>
+          <t>面积1</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>房间类型2</t>
+          <t>房间2</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>类型2</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>面积2</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
           <t>连接类型</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>连接数量</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>连接面积</t>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>数量</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>length</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>width</t>
         </is>
       </c>
     </row>
@@ -475,52 +490,70 @@
         </is>
       </c>
       <c r="C2" t="n">
+        <v>497516</v>
+      </c>
+      <c r="D2" t="n">
         <v>3</v>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>Bedroom</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>门/窗</t>
-        </is>
-      </c>
       <c r="F2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G2" t="n">
-        <v>913</v>
+        <v>129404</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>窗</t>
+        </is>
+      </c>
+      <c r="H2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I2" t="n">
+        <v>83</v>
+      </c>
+      <c r="J2" t="n">
+        <v>11</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Living Room</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>3</v>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Bedroom</t>
-        </is>
+        <v>129404</v>
+      </c>
+      <c r="D3" t="n">
+        <v>4</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>墙</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>346</v>
-      </c>
-      <c r="G3" t="n">
-        <v>3806</v>
+        <v>18437</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>窗</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I3" t="n">
+        <v>86</v>
+      </c>
+      <c r="J3" t="n">
+        <v>11</v>
       </c>
     </row>
     <row r="4">
@@ -533,115 +566,151 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>4</v>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Storage</t>
-        </is>
+        <v>129404</v>
+      </c>
+      <c r="D4" t="n">
+        <v>5</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>门/窗</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G4" t="n">
-        <v>946</v>
+        <v>19055</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>窗</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I4" t="n">
+        <v>72</v>
+      </c>
+      <c r="J4" t="n">
+        <v>11</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>4</v>
-      </c>
-      <c r="D5" t="inlineStr">
+        <v>119214</v>
+      </c>
+      <c r="D5" t="n">
+        <v>6</v>
+      </c>
+      <c r="E5" t="inlineStr">
         <is>
           <t>Storage</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>墙</t>
-        </is>
-      </c>
       <c r="F5" t="n">
-        <v>179</v>
-      </c>
-      <c r="G5" t="n">
-        <v>1969</v>
+        <v>14694</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>窗</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I5" t="n">
+        <v>93</v>
+      </c>
+      <c r="J5" t="n">
+        <v>11</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living Room</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>5</v>
-      </c>
-      <c r="D6" t="inlineStr">
+        <v>497516</v>
+      </c>
+      <c r="D6" t="n">
+        <v>7</v>
+      </c>
+      <c r="E6" t="inlineStr">
         <is>
           <t>Bath</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>门/窗</t>
-        </is>
-      </c>
       <c r="F6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G6" t="n">
-        <v>792</v>
+        <v>22680</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>窗</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I6" t="n">
+        <v>83</v>
+      </c>
+      <c r="J6" t="n">
+        <v>11</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>5</v>
-      </c>
-      <c r="D7" t="inlineStr">
+        <v>19055</v>
+      </c>
+      <c r="D7" t="n">
+        <v>10</v>
+      </c>
+      <c r="E7" t="inlineStr">
         <is>
           <t>Bath</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>墙</t>
-        </is>
-      </c>
       <c r="F7" t="n">
-        <v>185</v>
-      </c>
-      <c r="G7" t="n">
-        <v>2035</v>
+        <v>38570</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>窗</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I7" t="n">
+        <v>80</v>
+      </c>
+      <c r="J7" t="n">
+        <v>11</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -649,52 +718,70 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>6</v>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Storage</t>
-        </is>
+        <v>35164</v>
+      </c>
+      <c r="D8" t="n">
+        <v>10</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>门/窗</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1</v>
-      </c>
-      <c r="G8" t="n">
-        <v>1023</v>
+        <v>38570</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>窗</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>1</v>
+      </c>
+      <c r="I8" t="n">
+        <v>74</v>
+      </c>
+      <c r="J8" t="n">
+        <v>11</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>6</v>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Storage</t>
-        </is>
+        <v>14508</v>
+      </c>
+      <c r="D9" t="n">
+        <v>11</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>墙</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>186</v>
-      </c>
-      <c r="G9" t="n">
-        <v>2046</v>
+        <v>114872</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>窗</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>1</v>
+      </c>
+      <c r="I9" t="n">
+        <v>87</v>
+      </c>
+      <c r="J9" t="n">
+        <v>11</v>
       </c>
     </row>
     <row r="10">
@@ -707,115 +794,151 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>7</v>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Bath</t>
-        </is>
+        <v>497516</v>
+      </c>
+      <c r="D10" t="n">
+        <v>11</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>门/窗</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1</v>
-      </c>
-      <c r="G10" t="n">
-        <v>913</v>
+        <v>114872</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>窗</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I10" t="n">
+        <v>85</v>
+      </c>
+      <c r="J10" t="n">
+        <v>11</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Living Room</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>7</v>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Bath</t>
-        </is>
+        <v>38570</v>
+      </c>
+      <c r="D11" t="n">
+        <v>12</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>墙</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>168</v>
-      </c>
-      <c r="G11" t="n">
-        <v>1848</v>
+        <v>93202</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>窗</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>1</v>
+      </c>
+      <c r="I11" t="n">
+        <v>81</v>
+      </c>
+      <c r="J11" t="n">
+        <v>11</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Living Room</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>10</v>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Bath</t>
-        </is>
+        <v>497516</v>
+      </c>
+      <c r="D12" t="n">
+        <v>12</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>门/窗</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1</v>
-      </c>
-      <c r="G12" t="n">
-        <v>880</v>
+        <v>93202</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>窗</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I12" t="n">
+        <v>83</v>
+      </c>
+      <c r="J12" t="n">
+        <v>11</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Living Room</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>10</v>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Bath</t>
-        </is>
+        <v>497516</v>
+      </c>
+      <c r="D13" t="n">
+        <v>13</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>墙</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>176</v>
-      </c>
-      <c r="G13" t="n">
-        <v>1936</v>
+        <v>23166</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>窗</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I13" t="n">
+        <v>92</v>
+      </c>
+      <c r="J13" t="n">
+        <v>11</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -823,81 +946,108 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>10</v>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Bath</t>
-        </is>
+        <v>119214</v>
+      </c>
+      <c r="D14" t="n">
+        <v>6</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>门/窗</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1</v>
-      </c>
-      <c r="G14" t="n">
-        <v>814</v>
+        <v>14694</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>1</v>
+      </c>
+      <c r="I14" t="n">
+        <v>186</v>
+      </c>
+      <c r="J14" t="n">
+        <v>11</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>11</v>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
+        <v>119214</v>
+      </c>
+      <c r="D15" t="n">
+        <v>11</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>门/窗</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1</v>
-      </c>
-      <c r="G15" t="n">
-        <v>957</v>
+        <v>114872</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>1</v>
+      </c>
+      <c r="I15" t="n">
+        <v>190</v>
+      </c>
+      <c r="J15" t="n">
+        <v>11</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>11</v>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
+        <v>119214</v>
+      </c>
+      <c r="D16" t="n">
+        <v>7</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>墙</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>186</v>
-      </c>
-      <c r="G16" t="n">
-        <v>2046</v>
+        <v>22680</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>1</v>
+      </c>
+      <c r="I16" t="n">
+        <v>135</v>
+      </c>
+      <c r="J16" t="n">
+        <v>11</v>
       </c>
     </row>
     <row r="17">
@@ -910,23 +1060,32 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>11</v>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
+        <v>497516</v>
+      </c>
+      <c r="D17" t="n">
+        <v>3</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>门/窗</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1</v>
-      </c>
-      <c r="G17" t="n">
-        <v>935</v>
+        <v>129404</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I17" t="n">
+        <v>346</v>
+      </c>
+      <c r="J17" t="n">
+        <v>11</v>
       </c>
     </row>
     <row r="18">
@@ -939,81 +1098,108 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>11</v>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
+        <v>497516</v>
+      </c>
+      <c r="D18" t="n">
+        <v>4</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>墙</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>229</v>
-      </c>
-      <c r="G18" t="n">
-        <v>4818</v>
+        <v>18437</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H18" t="n">
+        <v>1</v>
+      </c>
+      <c r="I18" t="n">
+        <v>120</v>
+      </c>
+      <c r="J18" t="n">
+        <v>103</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
+          <t>Living Room</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>497516</v>
+      </c>
+      <c r="D19" t="n">
+        <v>7</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
           <t>Bath</t>
         </is>
       </c>
-      <c r="C19" t="n">
-        <v>12</v>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>门/窗</t>
-        </is>
-      </c>
       <c r="F19" t="n">
-        <v>1</v>
-      </c>
-      <c r="G19" t="n">
-        <v>891</v>
+        <v>22680</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H19" t="n">
+        <v>1</v>
+      </c>
+      <c r="I19" t="n">
+        <v>168</v>
+      </c>
+      <c r="J19" t="n">
+        <v>11</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Living Room</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>12</v>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
+        <v>497516</v>
+      </c>
+      <c r="D20" t="n">
+        <v>9</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>墙</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>203</v>
-      </c>
-      <c r="G20" t="n">
-        <v>2233</v>
+        <v>35164</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H20" t="n">
+        <v>1</v>
+      </c>
+      <c r="I20" t="n">
+        <v>270</v>
+      </c>
+      <c r="J20" t="n">
+        <v>49</v>
       </c>
     </row>
     <row r="21">
@@ -1026,23 +1212,32 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>12</v>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
+        <v>497516</v>
+      </c>
+      <c r="D21" t="n">
+        <v>11</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>门/窗</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1</v>
-      </c>
-      <c r="G21" t="n">
-        <v>913</v>
+        <v>114872</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I21" t="n">
+        <v>229</v>
+      </c>
+      <c r="J21" t="n">
+        <v>220</v>
       </c>
     </row>
     <row r="22">
@@ -1055,23 +1250,32 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>12</v>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
+        <v>497516</v>
+      </c>
+      <c r="D22" t="n">
+        <v>10</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>墙</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="F22" t="n">
+        <v>38570</v>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H22" t="n">
+        <v>1</v>
+      </c>
+      <c r="I22" t="n">
         <v>222</v>
       </c>
-      <c r="G22" t="n">
-        <v>2442</v>
+      <c r="J22" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="23">
@@ -1084,23 +1288,32 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>13</v>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>Hallway</t>
-        </is>
+        <v>497516</v>
+      </c>
+      <c r="D23" t="n">
+        <v>12</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>门/窗</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1</v>
-      </c>
-      <c r="G23" t="n">
-        <v>1012</v>
+        <v>93202</v>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H23" t="n">
+        <v>1</v>
+      </c>
+      <c r="I23" t="n">
+        <v>222</v>
+      </c>
+      <c r="J23" t="n">
+        <v>11</v>
       </c>
     </row>
     <row r="24">
@@ -1113,260 +1326,341 @@
         </is>
       </c>
       <c r="C24" t="n">
+        <v>497516</v>
+      </c>
+      <c r="D24" t="n">
         <v>13</v>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="E24" t="inlineStr">
         <is>
           <t>Hallway</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>墙</t>
-        </is>
-      </c>
       <c r="F24" t="n">
-        <v>315</v>
-      </c>
-      <c r="G24" t="n">
-        <v>3465</v>
+        <v>23166</v>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H24" t="n">
+        <v>1</v>
+      </c>
+      <c r="I24" t="n">
+        <v>209</v>
+      </c>
+      <c r="J24" t="n">
+        <v>128</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>11</v>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
+        <v>129404</v>
+      </c>
+      <c r="D25" t="n">
+        <v>4</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>墙</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>11</v>
-      </c>
-      <c r="G25" t="n">
-        <v>2090</v>
+        <v>18437</v>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H25" t="n">
+        <v>1</v>
+      </c>
+      <c r="I25" t="n">
+        <v>179</v>
+      </c>
+      <c r="J25" t="n">
+        <v>11</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>7</v>
-      </c>
-      <c r="D26" t="inlineStr">
+        <v>129404</v>
+      </c>
+      <c r="D26" t="n">
+        <v>10</v>
+      </c>
+      <c r="E26" t="inlineStr">
         <is>
           <t>Bath</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>墙</t>
-        </is>
-      </c>
       <c r="F26" t="n">
-        <v>135</v>
-      </c>
-      <c r="G26" t="n">
-        <v>1485</v>
+        <v>38570</v>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H26" t="n">
+        <v>1</v>
+      </c>
+      <c r="I26" t="n">
+        <v>125</v>
+      </c>
+      <c r="J26" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Living Room</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>4</v>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>Storage</t>
-        </is>
+        <v>129404</v>
+      </c>
+      <c r="D27" t="n">
+        <v>5</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>墙</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>103</v>
-      </c>
-      <c r="G27" t="n">
-        <v>5419</v>
+        <v>19055</v>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H27" t="n">
+        <v>1</v>
+      </c>
+      <c r="I27" t="n">
+        <v>185</v>
+      </c>
+      <c r="J27" t="n">
+        <v>11</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Living Room</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>9</v>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
+        <v>18437</v>
+      </c>
+      <c r="D28" t="n">
+        <v>5</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>墙</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>214</v>
-      </c>
-      <c r="G28" t="n">
-        <v>5671</v>
+        <v>19055</v>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H28" t="n">
+        <v>1</v>
+      </c>
+      <c r="I28" t="n">
+        <v>103</v>
+      </c>
+      <c r="J28" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Living Room</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>10</v>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>Bath</t>
-        </is>
+        <v>18437</v>
+      </c>
+      <c r="D29" t="n">
+        <v>9</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>墙</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>5</v>
-      </c>
-      <c r="G29" t="n">
-        <v>1110</v>
+        <v>35164</v>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H29" t="n">
+        <v>1</v>
+      </c>
+      <c r="I29" t="n">
+        <v>151</v>
+      </c>
+      <c r="J29" t="n">
+        <v>11</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="C30" t="n">
+        <v>18437</v>
+      </c>
+      <c r="D30" t="n">
         <v>10</v>
       </c>
-      <c r="D30" t="inlineStr">
+      <c r="E30" t="inlineStr">
         <is>
           <t>Bath</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>墙</t>
-        </is>
-      </c>
       <c r="F30" t="n">
-        <v>10</v>
-      </c>
-      <c r="G30" t="n">
-        <v>1250</v>
+        <v>38570</v>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H30" t="n">
+        <v>1</v>
+      </c>
+      <c r="I30" t="n">
+        <v>17</v>
+      </c>
+      <c r="J30" t="n">
+        <v>11</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>9</v>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
+        <v>19055</v>
+      </c>
+      <c r="D31" t="n">
+        <v>10</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>墙</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>151</v>
-      </c>
-      <c r="G31" t="n">
-        <v>1661</v>
+        <v>38570</v>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H31" t="n">
+        <v>1</v>
+      </c>
+      <c r="I31" t="n">
+        <v>176</v>
+      </c>
+      <c r="J31" t="n">
+        <v>11</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C32" t="n">
+        <v>19055</v>
+      </c>
+      <c r="D32" t="n">
         <v>12</v>
       </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>墙</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>11</v>
-      </c>
-      <c r="G32" t="n">
-        <v>3036</v>
+        <v>93202</v>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H32" t="n">
+        <v>1</v>
+      </c>
+      <c r="I32" t="n">
+        <v>212</v>
+      </c>
+      <c r="J32" t="n">
+        <v>9</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
@@ -1374,81 +1668,108 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>10</v>
-      </c>
-      <c r="D33" t="inlineStr">
+        <v>14694</v>
+      </c>
+      <c r="D33" t="n">
+        <v>7</v>
+      </c>
+      <c r="E33" t="inlineStr">
         <is>
           <t>Bath</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>墙</t>
-        </is>
-      </c>
       <c r="F33" t="n">
-        <v>17</v>
-      </c>
-      <c r="G33" t="n">
-        <v>187</v>
+        <v>22680</v>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H33" t="n">
+        <v>1</v>
+      </c>
+      <c r="I33" t="n">
+        <v>79</v>
+      </c>
+      <c r="J33" t="n">
+        <v>11</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>12</v>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
+        <v>14694</v>
+      </c>
+      <c r="D34" t="n">
+        <v>8</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>墙</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>9</v>
-      </c>
-      <c r="G34" t="n">
-        <v>1908</v>
+        <v>14508</v>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H34" t="n">
+        <v>1</v>
+      </c>
+      <c r="I34" t="n">
+        <v>186</v>
+      </c>
+      <c r="J34" t="n">
+        <v>11</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
+          <t>Bath</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>22680</v>
+      </c>
+      <c r="D35" t="n">
+        <v>8</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
           <t>Storage</t>
         </is>
       </c>
-      <c r="C35" t="n">
-        <v>8</v>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>Storage</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>墙</t>
-        </is>
-      </c>
       <c r="F35" t="n">
-        <v>186</v>
-      </c>
-      <c r="G35" t="n">
-        <v>2046</v>
+        <v>14508</v>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H35" t="n">
+        <v>1</v>
+      </c>
+      <c r="I35" t="n">
+        <v>78</v>
+      </c>
+      <c r="J35" t="n">
+        <v>11</v>
       </c>
     </row>
     <row r="36">
@@ -1461,57 +1782,75 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>11</v>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
+        <v>22680</v>
+      </c>
+      <c r="D36" t="n">
+        <v>11</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>墙</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="F36" t="n">
+        <v>114872</v>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H36" t="n">
+        <v>1</v>
+      </c>
+      <c r="I36" t="n">
         <v>135</v>
       </c>
-      <c r="G36" t="n">
-        <v>1485</v>
+      <c r="J36" t="n">
+        <v>11</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>12</v>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
+        <v>14508</v>
+      </c>
+      <c r="D37" t="n">
+        <v>11</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>墙</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>200</v>
-      </c>
-      <c r="G37" t="n">
-        <v>4190</v>
+        <v>114872</v>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H37" t="n">
+        <v>1</v>
+      </c>
+      <c r="I37" t="n">
+        <v>186</v>
+      </c>
+      <c r="J37" t="n">
+        <v>11</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
@@ -1519,23 +1858,146 @@
         </is>
       </c>
       <c r="C38" t="n">
+        <v>35164</v>
+      </c>
+      <c r="D38" t="n">
+        <v>10</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Bath</t>
+        </is>
+      </c>
+      <c r="F38" t="n">
+        <v>38570</v>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H38" t="n">
+        <v>1</v>
+      </c>
+      <c r="I38" t="n">
+        <v>185</v>
+      </c>
+      <c r="J38" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>9</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>35164</v>
+      </c>
+      <c r="D39" t="n">
+        <v>12</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="F39" t="n">
+        <v>93202</v>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H39" t="n">
+        <v>1</v>
+      </c>
+      <c r="I39" t="n">
+        <v>200</v>
+      </c>
+      <c r="J39" t="n">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>10</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Bath</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>38570</v>
+      </c>
+      <c r="D40" t="n">
+        <v>12</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="F40" t="n">
+        <v>93202</v>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H40" t="n">
+        <v>1</v>
+      </c>
+      <c r="I40" t="n">
+        <v>203</v>
+      </c>
+      <c r="J40" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>11</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>114872</v>
+      </c>
+      <c r="D41" t="n">
         <v>13</v>
       </c>
-      <c r="D38" t="inlineStr">
+      <c r="E41" t="inlineStr">
         <is>
           <t>Hallway</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>墙</t>
-        </is>
-      </c>
-      <c r="F38" t="n">
+      <c r="F41" t="n">
+        <v>23166</v>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H41" t="n">
+        <v>1</v>
+      </c>
+      <c r="I41" t="n">
         <v>117</v>
       </c>
-      <c r="G38" t="n">
-        <v>1287</v>
+      <c r="J41" t="n">
+        <v>11</v>
       </c>
     </row>
   </sheetData>

--- a/output/topology_excel/451.xlsx
+++ b/output/topology_excel/451.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J41"/>
+  <dimension ref="A1:J37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -505,7 +505,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>窗</t>
+          <t>门</t>
         </is>
       </c>
       <c r="H2" t="n">
@@ -543,7 +543,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>窗</t>
+          <t>门</t>
         </is>
       </c>
       <c r="H3" t="n">
@@ -581,7 +581,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>窗</t>
+          <t>门</t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -619,7 +619,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>窗</t>
+          <t>门</t>
         </is>
       </c>
       <c r="H5" t="n">
@@ -657,7 +657,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>窗</t>
+          <t>门</t>
         </is>
       </c>
       <c r="H6" t="n">
@@ -695,7 +695,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>窗</t>
+          <t>门</t>
         </is>
       </c>
       <c r="H7" t="n">
@@ -733,7 +733,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>窗</t>
+          <t>门</t>
         </is>
       </c>
       <c r="H8" t="n">
@@ -771,7 +771,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>窗</t>
+          <t>门</t>
         </is>
       </c>
       <c r="H9" t="n">
@@ -809,7 +809,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>窗</t>
+          <t>门</t>
         </is>
       </c>
       <c r="H10" t="n">
@@ -847,7 +847,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>窗</t>
+          <t>门</t>
         </is>
       </c>
       <c r="H11" t="n">
@@ -885,7 +885,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>窗</t>
+          <t>门</t>
         </is>
       </c>
       <c r="H12" t="n">
@@ -923,7 +923,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>窗</t>
+          <t>门</t>
         </is>
       </c>
       <c r="H13" t="n">
@@ -987,15 +987,15 @@
         <v>119214</v>
       </c>
       <c r="D15" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>114872</v>
+        <v>22680</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -1006,7 +1006,7 @@
         <v>1</v>
       </c>
       <c r="I15" t="n">
-        <v>190</v>
+        <v>135</v>
       </c>
       <c r="J15" t="n">
         <v>11</v>
@@ -1014,26 +1014,26 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Living Room</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>119214</v>
+        <v>497516</v>
       </c>
       <c r="D16" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>22680</v>
+        <v>129404</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -1044,7 +1044,7 @@
         <v>1</v>
       </c>
       <c r="I16" t="n">
-        <v>135</v>
+        <v>346</v>
       </c>
       <c r="J16" t="n">
         <v>11</v>
@@ -1063,15 +1063,15 @@
         <v>497516</v>
       </c>
       <c r="D17" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>129404</v>
+        <v>18437</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -1082,10 +1082,10 @@
         <v>1</v>
       </c>
       <c r="I17" t="n">
-        <v>346</v>
+        <v>103</v>
       </c>
       <c r="J17" t="n">
-        <v>11</v>
+        <v>60</v>
       </c>
     </row>
     <row r="18">
@@ -1101,15 +1101,15 @@
         <v>497516</v>
       </c>
       <c r="D18" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>18437</v>
+        <v>22680</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1120,10 +1120,10 @@
         <v>1</v>
       </c>
       <c r="I18" t="n">
-        <v>120</v>
+        <v>168</v>
       </c>
       <c r="J18" t="n">
-        <v>103</v>
+        <v>11</v>
       </c>
     </row>
     <row r="19">
@@ -1139,15 +1139,15 @@
         <v>497516</v>
       </c>
       <c r="D19" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>22680</v>
+        <v>35164</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1158,10 +1158,10 @@
         <v>1</v>
       </c>
       <c r="I19" t="n">
-        <v>168</v>
+        <v>270</v>
       </c>
       <c r="J19" t="n">
-        <v>11</v>
+        <v>49</v>
       </c>
     </row>
     <row r="20">
@@ -1177,7 +1177,7 @@
         <v>497516</v>
       </c>
       <c r="D20" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -1185,7 +1185,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>35164</v>
+        <v>114872</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1196,10 +1196,10 @@
         <v>1</v>
       </c>
       <c r="I20" t="n">
-        <v>270</v>
+        <v>218</v>
       </c>
       <c r="J20" t="n">
-        <v>49</v>
+        <v>11</v>
       </c>
     </row>
     <row r="21">
@@ -1215,7 +1215,7 @@
         <v>497516</v>
       </c>
       <c r="D21" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>114872</v>
+        <v>93202</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1234,10 +1234,10 @@
         <v>1</v>
       </c>
       <c r="I21" t="n">
-        <v>229</v>
+        <v>222</v>
       </c>
       <c r="J21" t="n">
-        <v>220</v>
+        <v>11</v>
       </c>
     </row>
     <row r="22">
@@ -1253,15 +1253,15 @@
         <v>497516</v>
       </c>
       <c r="D22" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>38570</v>
+        <v>23166</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1272,34 +1272,34 @@
         <v>1</v>
       </c>
       <c r="I22" t="n">
-        <v>222</v>
+        <v>209</v>
       </c>
       <c r="J22" t="n">
-        <v>5</v>
+        <v>128</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Living Room</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>497516</v>
+        <v>129404</v>
       </c>
       <c r="D23" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>93202</v>
+        <v>18437</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1310,7 +1310,7 @@
         <v>1</v>
       </c>
       <c r="I23" t="n">
-        <v>222</v>
+        <v>179</v>
       </c>
       <c r="J23" t="n">
         <v>11</v>
@@ -1318,26 +1318,26 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Living Room</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>497516</v>
+        <v>129404</v>
       </c>
       <c r="D24" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Hallway</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>23166</v>
+        <v>19055</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1348,34 +1348,34 @@
         <v>1</v>
       </c>
       <c r="I24" t="n">
-        <v>209</v>
+        <v>185</v>
       </c>
       <c r="J24" t="n">
-        <v>128</v>
+        <v>11</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>129404</v>
+        <v>18437</v>
       </c>
       <c r="D25" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>18437</v>
+        <v>19055</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1386,34 +1386,34 @@
         <v>1</v>
       </c>
       <c r="I25" t="n">
-        <v>179</v>
+        <v>103</v>
       </c>
       <c r="J25" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>129404</v>
+        <v>18437</v>
       </c>
       <c r="D26" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>38570</v>
+        <v>35164</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1424,26 +1424,26 @@
         <v>1</v>
       </c>
       <c r="I26" t="n">
-        <v>125</v>
+        <v>151</v>
       </c>
       <c r="J26" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>129404</v>
+        <v>18437</v>
       </c>
       <c r="D27" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -1451,7 +1451,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>19055</v>
+        <v>38570</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1462,7 +1462,7 @@
         <v>1</v>
       </c>
       <c r="I27" t="n">
-        <v>185</v>
+        <v>17</v>
       </c>
       <c r="J27" t="n">
         <v>11</v>
@@ -1470,18 +1470,18 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>18437</v>
+        <v>19055</v>
       </c>
       <c r="D28" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>19055</v>
+        <v>38570</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1500,15 +1500,15 @@
         <v>1</v>
       </c>
       <c r="I28" t="n">
-        <v>103</v>
+        <v>176</v>
       </c>
       <c r="J28" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
@@ -1516,18 +1516,18 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>18437</v>
+        <v>14694</v>
       </c>
       <c r="D29" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>35164</v>
+        <v>22680</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1538,7 +1538,7 @@
         <v>1</v>
       </c>
       <c r="I29" t="n">
-        <v>151</v>
+        <v>79</v>
       </c>
       <c r="J29" t="n">
         <v>11</v>
@@ -1546,7 +1546,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
@@ -1554,18 +1554,18 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>18437</v>
+        <v>14694</v>
       </c>
       <c r="D30" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>38570</v>
+        <v>14508</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1576,7 +1576,7 @@
         <v>1</v>
       </c>
       <c r="I30" t="n">
-        <v>17</v>
+        <v>186</v>
       </c>
       <c r="J30" t="n">
         <v>11</v>
@@ -1584,7 +1584,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
@@ -1592,18 +1592,18 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>19055</v>
+        <v>22680</v>
       </c>
       <c r="D31" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>38570</v>
+        <v>14508</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -1614,7 +1614,7 @@
         <v>1</v>
       </c>
       <c r="I31" t="n">
-        <v>176</v>
+        <v>78</v>
       </c>
       <c r="J31" t="n">
         <v>11</v>
@@ -1622,7 +1622,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
@@ -1630,10 +1630,10 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>19055</v>
+        <v>22680</v>
       </c>
       <c r="D32" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
@@ -1641,7 +1641,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>93202</v>
+        <v>114872</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -1652,15 +1652,15 @@
         <v>1</v>
       </c>
       <c r="I32" t="n">
-        <v>212</v>
+        <v>135</v>
       </c>
       <c r="J32" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
@@ -1668,18 +1668,18 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>14694</v>
+        <v>14508</v>
       </c>
       <c r="D33" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>22680</v>
+        <v>114872</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -1690,7 +1690,7 @@
         <v>1</v>
       </c>
       <c r="I33" t="n">
-        <v>79</v>
+        <v>186</v>
       </c>
       <c r="J33" t="n">
         <v>11</v>
@@ -1698,26 +1698,26 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>14694</v>
+        <v>35164</v>
       </c>
       <c r="D34" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>14508</v>
+        <v>38570</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -1728,34 +1728,34 @@
         <v>1</v>
       </c>
       <c r="I34" t="n">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="J34" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>22680</v>
+        <v>35164</v>
       </c>
       <c r="D35" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>14508</v>
+        <v>93202</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -1766,15 +1766,15 @@
         <v>1</v>
       </c>
       <c r="I35" t="n">
-        <v>78</v>
+        <v>190</v>
       </c>
       <c r="J35" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
@@ -1782,10 +1782,10 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>22680</v>
+        <v>38570</v>
       </c>
       <c r="D36" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
@@ -1793,7 +1793,7 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>114872</v>
+        <v>93202</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -1804,7 +1804,7 @@
         <v>1</v>
       </c>
       <c r="I36" t="n">
-        <v>135</v>
+        <v>203</v>
       </c>
       <c r="J36" t="n">
         <v>11</v>
@@ -1812,26 +1812,26 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>14508</v>
+        <v>114872</v>
       </c>
       <c r="D37" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>114872</v>
+        <v>23166</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -1842,161 +1842,9 @@
         <v>1</v>
       </c>
       <c r="I37" t="n">
-        <v>186</v>
+        <v>117</v>
       </c>
       <c r="J37" t="n">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="n">
-        <v>9</v>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="C38" t="n">
-        <v>35164</v>
-      </c>
-      <c r="D38" t="n">
-        <v>10</v>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>Bath</t>
-        </is>
-      </c>
-      <c r="F38" t="n">
-        <v>38570</v>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>墙</t>
-        </is>
-      </c>
-      <c r="H38" t="n">
-        <v>1</v>
-      </c>
-      <c r="I38" t="n">
-        <v>185</v>
-      </c>
-      <c r="J38" t="n">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="n">
-        <v>9</v>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="C39" t="n">
-        <v>35164</v>
-      </c>
-      <c r="D39" t="n">
-        <v>12</v>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="F39" t="n">
-        <v>93202</v>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>墙</t>
-        </is>
-      </c>
-      <c r="H39" t="n">
-        <v>1</v>
-      </c>
-      <c r="I39" t="n">
-        <v>200</v>
-      </c>
-      <c r="J39" t="n">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="n">
-        <v>10</v>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>Bath</t>
-        </is>
-      </c>
-      <c r="C40" t="n">
-        <v>38570</v>
-      </c>
-      <c r="D40" t="n">
-        <v>12</v>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="F40" t="n">
-        <v>93202</v>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>墙</t>
-        </is>
-      </c>
-      <c r="H40" t="n">
-        <v>1</v>
-      </c>
-      <c r="I40" t="n">
-        <v>203</v>
-      </c>
-      <c r="J40" t="n">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="n">
-        <v>11</v>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="C41" t="n">
-        <v>114872</v>
-      </c>
-      <c r="D41" t="n">
-        <v>13</v>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>Hallway</t>
-        </is>
-      </c>
-      <c r="F41" t="n">
-        <v>23166</v>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>墙</t>
-        </is>
-      </c>
-      <c r="H41" t="n">
-        <v>1</v>
-      </c>
-      <c r="I41" t="n">
-        <v>117</v>
-      </c>
-      <c r="J41" t="n">
         <v>11</v>
       </c>
     </row>

--- a/output/topology_excel/451.xlsx
+++ b/output/topology_excel/451.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F37"/>
+  <dimension ref="A1:F46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -487,7 +487,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -509,7 +509,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -528,10 +528,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="B5" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -550,7 +550,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="B6" t="n">
         <v>7</v>
@@ -572,10 +572,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B7" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -594,10 +594,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -616,10 +616,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B9" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -638,10 +638,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="B10" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -660,10 +660,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="B11" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -682,10 +682,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B12" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -704,10 +704,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="B13" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -729,7 +729,7 @@
         <v>1</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -740,10 +740,10 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>186</v>
+        <v>373</v>
       </c>
       <c r="F14" t="n">
-        <v>11</v>
+        <v>71</v>
       </c>
     </row>
     <row r="15">
@@ -751,7 +751,7 @@
         <v>1</v>
       </c>
       <c r="B15" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -762,18 +762,18 @@
         <v>1</v>
       </c>
       <c r="E15" t="n">
-        <v>135</v>
+        <v>63</v>
       </c>
       <c r="F15" t="n">
-        <v>11</v>
+        <v>60</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>1</v>
       </c>
       <c r="E16" t="n">
-        <v>346</v>
+        <v>368</v>
       </c>
       <c r="F16" t="n">
         <v>11</v>
@@ -792,10 +792,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B17" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -806,18 +806,18 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>103</v>
+        <v>185</v>
       </c>
       <c r="F17" t="n">
-        <v>60</v>
+        <v>16</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B18" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -828,7 +828,7 @@
         <v>1</v>
       </c>
       <c r="E18" t="n">
-        <v>168</v>
+        <v>222</v>
       </c>
       <c r="F18" t="n">
         <v>11</v>
@@ -836,10 +836,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B19" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -850,10 +850,10 @@
         <v>1</v>
       </c>
       <c r="E19" t="n">
-        <v>270</v>
+        <v>117</v>
       </c>
       <c r="F19" t="n">
-        <v>49</v>
+        <v>11</v>
       </c>
     </row>
     <row r="20">
@@ -861,7 +861,7 @@
         <v>2</v>
       </c>
       <c r="B20" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>218</v>
+        <v>346</v>
       </c>
       <c r="F20" t="n">
         <v>11</v>
@@ -883,7 +883,7 @@
         <v>2</v>
       </c>
       <c r="B21" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -894,7 +894,7 @@
         <v>1</v>
       </c>
       <c r="E21" t="n">
-        <v>222</v>
+        <v>29</v>
       </c>
       <c r="F21" t="n">
         <v>11</v>
@@ -905,7 +905,7 @@
         <v>2</v>
       </c>
       <c r="B22" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -916,18 +916,18 @@
         <v>1</v>
       </c>
       <c r="E22" t="n">
-        <v>209</v>
+        <v>18</v>
       </c>
       <c r="F22" t="n">
-        <v>128</v>
+        <v>11</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B23" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -938,10 +938,10 @@
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>179</v>
+        <v>85</v>
       </c>
       <c r="F23" t="n">
-        <v>11</v>
+        <v>38</v>
       </c>
     </row>
     <row r="24">
@@ -949,7 +949,7 @@
         <v>3</v>
       </c>
       <c r="B24" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -960,7 +960,7 @@
         <v>1</v>
       </c>
       <c r="E24" t="n">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="F24" t="n">
         <v>11</v>
@@ -968,11 +968,11 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
+        <v>3</v>
+      </c>
+      <c r="B25" t="n">
         <v>4</v>
       </c>
-      <c r="B25" t="n">
-        <v>5</v>
-      </c>
       <c r="C25" t="inlineStr">
         <is>
           <t>Wall</t>
@@ -982,10 +982,10 @@
         <v>1</v>
       </c>
       <c r="E25" t="n">
-        <v>103</v>
+        <v>185</v>
       </c>
       <c r="F25" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="26">
@@ -1004,10 +1004,10 @@
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>151</v>
+        <v>103</v>
       </c>
       <c r="F26" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="27">
@@ -1015,7 +1015,7 @@
         <v>4</v>
       </c>
       <c r="B27" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -1026,7 +1026,7 @@
         <v>1</v>
       </c>
       <c r="E27" t="n">
-        <v>17</v>
+        <v>176</v>
       </c>
       <c r="F27" t="n">
         <v>11</v>
@@ -1037,7 +1037,7 @@
         <v>5</v>
       </c>
       <c r="B28" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -1048,7 +1048,7 @@
         <v>1</v>
       </c>
       <c r="E28" t="n">
-        <v>176</v>
+        <v>135</v>
       </c>
       <c r="F28" t="n">
         <v>11</v>
@@ -1056,10 +1056,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B29" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -1078,10 +1078,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B30" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -1092,7 +1092,7 @@
         <v>1</v>
       </c>
       <c r="E30" t="n">
-        <v>186</v>
+        <v>150</v>
       </c>
       <c r="F30" t="n">
         <v>11</v>
@@ -1100,10 +1100,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B31" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -1122,10 +1122,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B32" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -1144,10 +1144,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B33" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -1158,7 +1158,7 @@
         <v>1</v>
       </c>
       <c r="E33" t="n">
-        <v>186</v>
+        <v>17</v>
       </c>
       <c r="F33" t="n">
         <v>11</v>
@@ -1166,10 +1166,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B34" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -1188,10 +1188,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B35" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -1202,18 +1202,18 @@
         <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>190</v>
+        <v>203</v>
       </c>
       <c r="F35" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B36" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -1224,7 +1224,7 @@
         <v>1</v>
       </c>
       <c r="E36" t="n">
-        <v>203</v>
+        <v>218</v>
       </c>
       <c r="F36" t="n">
         <v>11</v>
@@ -1232,24 +1232,222 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B37" t="n">
+        <v>8</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>1</v>
+      </c>
+      <c r="E37" t="n">
+        <v>198</v>
+      </c>
+      <c r="F37" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>8</v>
+      </c>
+      <c r="B38" t="n">
+        <v>14</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>1</v>
+      </c>
+      <c r="E38" t="n">
+        <v>117</v>
+      </c>
+      <c r="F38" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>9</v>
+      </c>
+      <c r="B39" t="n">
         <v>13</v>
       </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Wall</t>
-        </is>
-      </c>
-      <c r="D37" t="n">
-        <v>1</v>
-      </c>
-      <c r="E37" t="n">
-        <v>117</v>
-      </c>
-      <c r="F37" t="n">
-        <v>11</v>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>1</v>
+      </c>
+      <c r="E39" t="n">
+        <v>151</v>
+      </c>
+      <c r="F39" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>10</v>
+      </c>
+      <c r="B40" t="n">
+        <v>12</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>1</v>
+      </c>
+      <c r="E40" t="n">
+        <v>186</v>
+      </c>
+      <c r="F40" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>10</v>
+      </c>
+      <c r="B41" t="n">
+        <v>11</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>1</v>
+      </c>
+      <c r="E41" t="n">
+        <v>186</v>
+      </c>
+      <c r="F41" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>11</v>
+      </c>
+      <c r="B42" t="n">
+        <v>14</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>1</v>
+      </c>
+      <c r="E42" t="n">
+        <v>186</v>
+      </c>
+      <c r="F42" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>13</v>
+      </c>
+      <c r="B43" t="n">
+        <v>15</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>1</v>
+      </c>
+      <c r="E43" t="n">
+        <v>190</v>
+      </c>
+      <c r="F43" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>2</v>
+      </c>
+      <c r="B44" t="n">
+        <v>7</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>1</v>
+      </c>
+      <c r="E44" t="n">
+        <v>198</v>
+      </c>
+      <c r="F44" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>1</v>
+      </c>
+      <c r="B45" t="n">
+        <v>2</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>1</v>
+      </c>
+      <c r="E45" t="n">
+        <v>104</v>
+      </c>
+      <c r="F45" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>1</v>
+      </c>
+      <c r="B46" t="n">
+        <v>7</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>1</v>
+      </c>
+      <c r="E46" t="n">
+        <v>139</v>
+      </c>
+      <c r="F46" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/output/topology_excel/451.xlsx
+++ b/output/topology_excel/451.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F46"/>
+  <dimension ref="A1:H46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,12 +451,22 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Length</t>
+          <t>Length_1</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Width</t>
+          <t>Width_1</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Length_2</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Width_2</t>
         </is>
       </c>
     </row>
@@ -481,6 +491,8 @@
       <c r="F2" t="n">
         <v>11</v>
       </c>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -503,6 +515,8 @@
       <c r="F3" t="n">
         <v>11</v>
       </c>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -525,6 +539,8 @@
       <c r="F4" t="n">
         <v>11</v>
       </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -547,6 +563,8 @@
       <c r="F5" t="n">
         <v>11</v>
       </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -569,6 +587,8 @@
       <c r="F6" t="n">
         <v>11</v>
       </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -591,6 +611,8 @@
       <c r="F7" t="n">
         <v>11</v>
       </c>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -613,6 +635,8 @@
       <c r="F8" t="n">
         <v>11</v>
       </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -635,6 +659,8 @@
       <c r="F9" t="n">
         <v>11</v>
       </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -657,6 +683,8 @@
       <c r="F10" t="n">
         <v>11</v>
       </c>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -679,6 +707,8 @@
       <c r="F11" t="n">
         <v>11</v>
       </c>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -701,6 +731,8 @@
       <c r="F12" t="n">
         <v>11</v>
       </c>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -723,6 +755,8 @@
       <c r="F13" t="n">
         <v>11</v>
       </c>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -737,13 +771,19 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E14" t="n">
-        <v>373</v>
+        <v>60</v>
       </c>
       <c r="F14" t="n">
-        <v>71</v>
+        <v>11</v>
+      </c>
+      <c r="G14" t="n">
+        <v>209</v>
+      </c>
+      <c r="H14" t="n">
+        <v>14</v>
       </c>
     </row>
     <row r="15">
@@ -767,6 +807,8 @@
       <c r="F15" t="n">
         <v>60</v>
       </c>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -781,12 +823,18 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E16" t="n">
-        <v>368</v>
+        <v>59</v>
       </c>
       <c r="F16" t="n">
+        <v>11</v>
+      </c>
+      <c r="G16" t="n">
+        <v>170</v>
+      </c>
+      <c r="H16" t="n">
         <v>11</v>
       </c>
     </row>
@@ -803,13 +851,19 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E17" t="n">
-        <v>185</v>
+        <v>61</v>
       </c>
       <c r="F17" t="n">
-        <v>16</v>
+        <v>11</v>
+      </c>
+      <c r="G17" t="n">
+        <v>115</v>
+      </c>
+      <c r="H17" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="18">
@@ -833,6 +887,8 @@
       <c r="F18" t="n">
         <v>11</v>
       </c>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -855,6 +911,8 @@
       <c r="F19" t="n">
         <v>11</v>
       </c>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -877,6 +935,8 @@
       <c r="F20" t="n">
         <v>11</v>
       </c>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -899,6 +959,8 @@
       <c r="F21" t="n">
         <v>11</v>
       </c>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -921,6 +983,8 @@
       <c r="F22" t="n">
         <v>11</v>
       </c>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -943,6 +1007,8 @@
       <c r="F23" t="n">
         <v>38</v>
       </c>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -965,6 +1031,8 @@
       <c r="F24" t="n">
         <v>11</v>
       </c>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -987,6 +1055,8 @@
       <c r="F25" t="n">
         <v>11</v>
       </c>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -1009,6 +1079,8 @@
       <c r="F26" t="n">
         <v>10</v>
       </c>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -1031,6 +1103,8 @@
       <c r="F27" t="n">
         <v>11</v>
       </c>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -1053,6 +1127,8 @@
       <c r="F28" t="n">
         <v>11</v>
       </c>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -1075,6 +1151,8 @@
       <c r="F29" t="n">
         <v>11</v>
       </c>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -1097,6 +1175,8 @@
       <c r="F30" t="n">
         <v>11</v>
       </c>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -1119,6 +1199,8 @@
       <c r="F31" t="n">
         <v>11</v>
       </c>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -1141,6 +1223,8 @@
       <c r="F32" t="n">
         <v>11</v>
       </c>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -1163,6 +1247,8 @@
       <c r="F33" t="n">
         <v>11</v>
       </c>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -1183,8 +1269,10 @@
         <v>185</v>
       </c>
       <c r="F34" t="n">
-        <v>16</v>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -1207,6 +1295,8 @@
       <c r="F35" t="n">
         <v>11</v>
       </c>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -1229,6 +1319,8 @@
       <c r="F36" t="n">
         <v>11</v>
       </c>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -1251,6 +1343,8 @@
       <c r="F37" t="n">
         <v>11</v>
       </c>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -1273,6 +1367,8 @@
       <c r="F38" t="n">
         <v>11</v>
       </c>
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -1295,6 +1391,8 @@
       <c r="F39" t="n">
         <v>11</v>
       </c>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -1317,6 +1415,8 @@
       <c r="F40" t="n">
         <v>11</v>
       </c>
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -1339,6 +1439,8 @@
       <c r="F41" t="n">
         <v>11</v>
       </c>
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -1361,6 +1463,8 @@
       <c r="F42" t="n">
         <v>11</v>
       </c>
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -1383,6 +1487,8 @@
       <c r="F43" t="n">
         <v>16</v>
       </c>
+      <c r="G43" t="inlineStr"/>
+      <c r="H43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -1405,6 +1511,8 @@
       <c r="F44" t="n">
         <v>1</v>
       </c>
+      <c r="G44" t="inlineStr"/>
+      <c r="H44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -1427,6 +1535,8 @@
       <c r="F45" t="n">
         <v>1</v>
       </c>
+      <c r="G45" t="inlineStr"/>
+      <c r="H45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -1449,6 +1559,8 @@
       <c r="F46" t="n">
         <v>1</v>
       </c>
+      <c r="G46" t="inlineStr"/>
+      <c r="H46" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
